--- a/jscode/TestData.xlsx
+++ b/jscode/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PLaywrightwithjavascriptaug26\javascriptaug26\jscode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AC3C94-6E1E-4F63-B80E-0CBF5F90AC95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9354BE0D-4A7E-439D-9D48-FEC0CEBEC58A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
